--- a/Employee_Reports_wi48/Jeffrey De Vera Cabico Q0617.xlsx
+++ b/Employee_Reports_wi48/Jeffrey De Vera Cabico Q0617.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1330,11 +1330,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1379,11 +1379,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1428,11 +1428,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1477,11 +1477,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1514,11 +1514,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1563,11 +1563,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1661,11 +1661,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
